--- a/output/yearly_total_coral_cover_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_46_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.267256071876949</v>
+        <v>1.262808754776711</v>
       </c>
       <c r="C3" t="n">
-        <v>4.607888700561708</v>
+        <v>4.591375704176277</v>
       </c>
       <c r="D3" t="n">
-        <v>6.128967562992616</v>
+        <v>6.028083168904215</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00411233543127</v>
+        <v>11.8822676278572</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.414538336045168</v>
+        <v>1.398036472072356</v>
       </c>
       <c r="C4" t="n">
-        <v>5.073715775166021</v>
+        <v>5.005289646766666</v>
       </c>
       <c r="D4" t="n">
-        <v>6.468485210350292</v>
+        <v>6.255310978543041</v>
       </c>
       <c r="E4" t="n">
-        <v>12.95673932156148</v>
+        <v>12.65863709738206</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.610348788739146</v>
+        <v>1.57984822531473</v>
       </c>
       <c r="C5" t="n">
-        <v>5.643717095303995</v>
+        <v>5.489032534745469</v>
       </c>
       <c r="D5" t="n">
-        <v>6.83681925321314</v>
+        <v>6.491663604732347</v>
       </c>
       <c r="E5" t="n">
-        <v>14.09088513725628</v>
+        <v>13.56054436479255</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.833238995037746</v>
+        <v>1.789507913221103</v>
       </c>
       <c r="C6" t="n">
-        <v>6.317627599771137</v>
+        <v>6.106870816730671</v>
       </c>
       <c r="D6" t="n">
-        <v>7.188605049776366</v>
+        <v>6.799910871461154</v>
       </c>
       <c r="E6" t="n">
-        <v>15.33947164458525</v>
+        <v>14.69628960141293</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.082284918105142</v>
+        <v>2.049861891326493</v>
       </c>
       <c r="C7" t="n">
-        <v>7.118741714611447</v>
+        <v>6.863895070034845</v>
       </c>
       <c r="D7" t="n">
-        <v>7.642270359845224</v>
+        <v>7.1307097470065</v>
       </c>
       <c r="E7" t="n">
-        <v>16.84329699256181</v>
+        <v>16.04446670836784</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.306890264704487</v>
+        <v>1.288370230138612</v>
       </c>
       <c r="C8" t="n">
-        <v>4.764393621422896</v>
+        <v>4.616879490109572</v>
       </c>
       <c r="D8" t="n">
-        <v>5.859427098287124</v>
+        <v>5.423336164437399</v>
       </c>
       <c r="E8" t="n">
-        <v>11.93071098441451</v>
+        <v>11.32858588468558</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.656677058784677</v>
+        <v>1.655083975985546</v>
       </c>
       <c r="C9" t="n">
-        <v>5.791348582464303</v>
+        <v>5.748319221342446</v>
       </c>
       <c r="D9" t="n">
-        <v>6.406601347566416</v>
+        <v>5.949709279684458</v>
       </c>
       <c r="E9" t="n">
-        <v>13.8546269888154</v>
+        <v>13.35311247701245</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.025230407544314</v>
+        <v>2.044342728956413</v>
       </c>
       <c r="C10" t="n">
-        <v>6.956094890270743</v>
+        <v>7.0698201792809</v>
       </c>
       <c r="D10" t="n">
-        <v>6.913718817267688</v>
+        <v>6.4269626554846</v>
       </c>
       <c r="E10" t="n">
-        <v>15.89504411508274</v>
+        <v>15.54112556372191</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.394329288670678</v>
+        <v>2.452717239768758</v>
       </c>
       <c r="C11" t="n">
-        <v>8.228912444735636</v>
+        <v>8.523769990075301</v>
       </c>
       <c r="D11" t="n">
-        <v>7.536586318836877</v>
+        <v>7.02892888769386</v>
       </c>
       <c r="E11" t="n">
-        <v>18.15982805224319</v>
+        <v>18.00541611753792</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.757398289745481</v>
+        <v>2.868916478298094</v>
       </c>
       <c r="C12" t="n">
-        <v>9.558852498235394</v>
+        <v>10.05325641289943</v>
       </c>
       <c r="D12" t="n">
-        <v>8.054536185575611</v>
+        <v>7.51469493934035</v>
       </c>
       <c r="E12" t="n">
-        <v>20.37078697355648</v>
+        <v>20.43686783053787</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.110015264078913</v>
+        <v>3.280644420916208</v>
       </c>
       <c r="C13" t="n">
-        <v>10.97651174187413</v>
+        <v>11.66457365582306</v>
       </c>
       <c r="D13" t="n">
-        <v>8.665861871254632</v>
+        <v>8.142670269818534</v>
       </c>
       <c r="E13" t="n">
-        <v>22.75238887720767</v>
+        <v>23.0878883465578</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.791169233967178</v>
+        <v>1.888656780998887</v>
       </c>
       <c r="C14" t="n">
-        <v>7.752174397044089</v>
+        <v>8.104867259794755</v>
       </c>
       <c r="D14" t="n">
-        <v>6.565300327471951</v>
+        <v>6.243925216486756</v>
       </c>
       <c r="E14" t="n">
-        <v>16.10864395848322</v>
+        <v>16.2374492572804</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.833600369744725</v>
+        <v>1.970446182239688</v>
       </c>
       <c r="C15" t="n">
-        <v>8.335980486851497</v>
+        <v>8.859242195738004</v>
       </c>
       <c r="D15" t="n">
-        <v>6.633767412366123</v>
+        <v>6.309162351433957</v>
       </c>
       <c r="E15" t="n">
-        <v>16.80334826896235</v>
+        <v>17.13885072941165</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.12307849781894</v>
+        <v>2.312123835748706</v>
       </c>
       <c r="C16" t="n">
-        <v>9.846006630753516</v>
+        <v>10.53897324779613</v>
       </c>
       <c r="D16" t="n">
-        <v>7.188592309944165</v>
+        <v>6.805102021711276</v>
       </c>
       <c r="E16" t="n">
-        <v>19.15767743851662</v>
+        <v>19.65619910525611</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.698943854630233</v>
+        <v>1.869925034801857</v>
       </c>
       <c r="C17" t="n">
-        <v>9.105543059779444</v>
+        <v>9.847439982401717</v>
       </c>
       <c r="D17" t="n">
-        <v>6.738843869151659</v>
+        <v>6.338752227239957</v>
       </c>
       <c r="E17" t="n">
-        <v>17.54333078356134</v>
+        <v>18.05611724444353</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.938765183823644</v>
+        <v>2.145089281348153</v>
       </c>
       <c r="C18" t="n">
-        <v>10.62087064128439</v>
+        <v>11.48729244271333</v>
       </c>
       <c r="D18" t="n">
-        <v>7.245995098211477</v>
+        <v>6.787136038723561</v>
       </c>
       <c r="E18" t="n">
-        <v>19.80563092331952</v>
+        <v>20.41951776278505</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.946206831421835</v>
+        <v>2.159727139618473</v>
       </c>
       <c r="C19" t="n">
-        <v>11.3661742284404</v>
+        <v>12.29115728042766</v>
       </c>
       <c r="D19" t="n">
-        <v>7.40265257937814</v>
+        <v>6.909118190976226</v>
       </c>
       <c r="E19" t="n">
-        <v>20.71503363924038</v>
+        <v>21.36000261102236</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.175778714582909</v>
+        <v>2.416601426434652</v>
       </c>
       <c r="C20" t="n">
-        <v>13.06561877439981</v>
+        <v>14.07118367795164</v>
       </c>
       <c r="D20" t="n">
-        <v>7.95058560807237</v>
+        <v>7.4501495333096</v>
       </c>
       <c r="E20" t="n">
-        <v>23.19198309705508</v>
+        <v>23.93793463769589</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.299441261341078</v>
+        <v>1.437425901172968</v>
       </c>
       <c r="C21" t="n">
-        <v>9.624799238032624</v>
+        <v>10.23849954543435</v>
       </c>
       <c r="D21" t="n">
-        <v>6.66549749816738</v>
+        <v>6.261017444017694</v>
       </c>
       <c r="E21" t="n">
-        <v>17.58973799754108</v>
+        <v>17.93694289062501</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_46_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.262808754776711</v>
+        <v>1.252873468009733</v>
       </c>
       <c r="C3" t="n">
-        <v>4.591375704176277</v>
+        <v>4.619532228334076</v>
       </c>
       <c r="D3" t="n">
-        <v>6.028083168904215</v>
+        <v>6.051409494357118</v>
       </c>
       <c r="E3" t="n">
-        <v>11.8822676278572</v>
+        <v>11.92381519070093</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.398036472072356</v>
+        <v>1.385659294989731</v>
       </c>
       <c r="C4" t="n">
-        <v>5.005289646766666</v>
+        <v>5.130758809465148</v>
       </c>
       <c r="D4" t="n">
-        <v>6.255310978543041</v>
+        <v>6.330600368098304</v>
       </c>
       <c r="E4" t="n">
-        <v>12.65863709738206</v>
+        <v>12.84701847255318</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.57984822531473</v>
+        <v>1.564449472170686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.489032534745469</v>
+        <v>5.777890902941534</v>
       </c>
       <c r="D5" t="n">
-        <v>6.491663604732347</v>
+        <v>6.587168529604914</v>
       </c>
       <c r="E5" t="n">
-        <v>13.56054436479255</v>
+        <v>13.92950890471714</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.789507913221103</v>
+        <v>1.77140125319316</v>
       </c>
       <c r="C6" t="n">
-        <v>6.106870816730671</v>
+        <v>6.603692013994531</v>
       </c>
       <c r="D6" t="n">
-        <v>6.799910871461154</v>
+        <v>6.97151350996878</v>
       </c>
       <c r="E6" t="n">
-        <v>14.69628960141293</v>
+        <v>15.34660677715647</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.049861891326493</v>
+        <v>2.006362808776009</v>
       </c>
       <c r="C7" t="n">
-        <v>6.863895070034845</v>
+        <v>7.582733598957394</v>
       </c>
       <c r="D7" t="n">
-        <v>7.1307097470065</v>
+        <v>7.379168473184678</v>
       </c>
       <c r="E7" t="n">
-        <v>16.04446670836784</v>
+        <v>16.96826488091808</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.288370230138612</v>
+        <v>1.236940843785439</v>
       </c>
       <c r="C8" t="n">
-        <v>4.616879490109572</v>
+        <v>5.324289916760494</v>
       </c>
       <c r="D8" t="n">
-        <v>5.423336164437399</v>
+        <v>5.608374344899554</v>
       </c>
       <c r="E8" t="n">
-        <v>11.32858588468558</v>
+        <v>12.16960510544549</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.655083975985546</v>
+        <v>1.547406960580967</v>
       </c>
       <c r="C9" t="n">
-        <v>5.748319221342446</v>
+        <v>6.657909340123153</v>
       </c>
       <c r="D9" t="n">
-        <v>5.949709279684458</v>
+        <v>6.074522258392176</v>
       </c>
       <c r="E9" t="n">
-        <v>13.35311247701245</v>
+        <v>14.2798385590963</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.044342728956413</v>
+        <v>1.878008470427901</v>
       </c>
       <c r="C10" t="n">
-        <v>7.0698201792809</v>
+        <v>8.26631348934251</v>
       </c>
       <c r="D10" t="n">
-        <v>6.4269626554846</v>
+        <v>6.554524389699413</v>
       </c>
       <c r="E10" t="n">
-        <v>15.54112556372191</v>
+        <v>16.69884634946983</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.452717239768758</v>
+        <v>2.200947795875413</v>
       </c>
       <c r="C11" t="n">
-        <v>8.523769990075301</v>
+        <v>10.02430975314422</v>
       </c>
       <c r="D11" t="n">
-        <v>7.02892888769386</v>
+        <v>7.055606378590482</v>
       </c>
       <c r="E11" t="n">
-        <v>18.00541611753792</v>
+        <v>19.28086392761012</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.868916478298094</v>
+        <v>2.527014246588251</v>
       </c>
       <c r="C12" t="n">
-        <v>10.05325641289943</v>
+        <v>11.84646304674301</v>
       </c>
       <c r="D12" t="n">
-        <v>7.51469493934035</v>
+        <v>7.568221353889825</v>
       </c>
       <c r="E12" t="n">
-        <v>20.43686783053787</v>
+        <v>21.94169864722109</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.280644420916208</v>
+        <v>2.836040039274214</v>
       </c>
       <c r="C13" t="n">
-        <v>11.66457365582306</v>
+        <v>13.67912677020678</v>
       </c>
       <c r="D13" t="n">
-        <v>8.142670269818534</v>
+        <v>8.049143663896318</v>
       </c>
       <c r="E13" t="n">
-        <v>23.0878883465578</v>
+        <v>24.56431047337731</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.888656780998887</v>
+        <v>1.63357909248148</v>
       </c>
       <c r="C14" t="n">
-        <v>8.104867259794755</v>
+        <v>9.445522289760115</v>
       </c>
       <c r="D14" t="n">
-        <v>6.243925216486756</v>
+        <v>6.124073456752305</v>
       </c>
       <c r="E14" t="n">
-        <v>16.2374492572804</v>
+        <v>17.2031748389939</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.970446182239688</v>
+        <v>1.666938879471787</v>
       </c>
       <c r="C15" t="n">
-        <v>8.859242195738004</v>
+        <v>10.33902069287218</v>
       </c>
       <c r="D15" t="n">
-        <v>6.309162351433957</v>
+        <v>6.146329677207581</v>
       </c>
       <c r="E15" t="n">
-        <v>17.13885072941165</v>
+        <v>18.15228924955155</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.312123835748706</v>
+        <v>1.926012281145477</v>
       </c>
       <c r="C16" t="n">
-        <v>10.53897324779613</v>
+        <v>12.22708842524852</v>
       </c>
       <c r="D16" t="n">
-        <v>6.805102021711276</v>
+        <v>6.682314836341128</v>
       </c>
       <c r="E16" t="n">
-        <v>19.65619910525611</v>
+        <v>20.83541554273512</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.869925034801857</v>
+        <v>1.543425200800495</v>
       </c>
       <c r="C17" t="n">
-        <v>9.847439982401717</v>
+        <v>11.27595161442012</v>
       </c>
       <c r="D17" t="n">
-        <v>6.338752227239957</v>
+        <v>6.222012607727968</v>
       </c>
       <c r="E17" t="n">
-        <v>18.05611724444353</v>
+        <v>19.04138942294859</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.145089281348153</v>
+        <v>1.745783037599848</v>
       </c>
       <c r="C18" t="n">
-        <v>11.48729244271333</v>
+        <v>13.11639476566345</v>
       </c>
       <c r="D18" t="n">
-        <v>6.787136038723561</v>
+        <v>6.654884805484473</v>
       </c>
       <c r="E18" t="n">
-        <v>20.41951776278505</v>
+        <v>21.51706260874777</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.159727139618473</v>
+        <v>1.739892551374367</v>
       </c>
       <c r="C19" t="n">
-        <v>12.29115728042766</v>
+        <v>13.97316598715964</v>
       </c>
       <c r="D19" t="n">
-        <v>6.909118190976226</v>
+        <v>6.76649970198029</v>
       </c>
       <c r="E19" t="n">
-        <v>21.36000261102236</v>
+        <v>22.4795582405143</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.416601426434652</v>
+        <v>1.92140788441256</v>
       </c>
       <c r="C20" t="n">
-        <v>14.07118367795164</v>
+        <v>16.03745743244828</v>
       </c>
       <c r="D20" t="n">
-        <v>7.4501495333096</v>
+        <v>7.196927347953221</v>
       </c>
       <c r="E20" t="n">
-        <v>23.93793463769589</v>
+        <v>25.15579266481406</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.437425901172968</v>
+        <v>1.132151452537422</v>
       </c>
       <c r="C21" t="n">
-        <v>10.23849954543435</v>
+        <v>11.7200746408673</v>
       </c>
       <c r="D21" t="n">
-        <v>6.261017444017694</v>
+        <v>6.023041800508268</v>
       </c>
       <c r="E21" t="n">
-        <v>17.93694289062501</v>
+        <v>18.87526789391299</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_46_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252873468009733</v>
+        <v>2.579109645802156</v>
       </c>
       <c r="C3" t="n">
-        <v>4.619532228334076</v>
+        <v>7.86246110349568</v>
       </c>
       <c r="D3" t="n">
-        <v>6.051409494357118</v>
+        <v>8.218080210105919</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92381519070093</v>
+        <v>18.65965095940376</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.385659294989731</v>
+        <v>1.038053092736938</v>
       </c>
       <c r="C4" t="n">
-        <v>5.130758809465148</v>
+        <v>4.875750438845182</v>
       </c>
       <c r="D4" t="n">
-        <v>6.330600368098304</v>
+        <v>5.903453947500461</v>
       </c>
       <c r="E4" t="n">
-        <v>12.84701847255318</v>
+        <v>11.81725747908258</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.564449472170686</v>
+        <v>1.091837765666164</v>
       </c>
       <c r="C5" t="n">
-        <v>5.777890902941534</v>
+        <v>5.976425361571787</v>
       </c>
       <c r="D5" t="n">
-        <v>6.587168529604914</v>
+        <v>6.217850784678685</v>
       </c>
       <c r="E5" t="n">
-        <v>13.92950890471714</v>
+        <v>13.28611391191663</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.77140125319316</v>
+        <v>1.148206496314971</v>
       </c>
       <c r="C6" t="n">
-        <v>6.603692013994531</v>
+        <v>7.364986984959453</v>
       </c>
       <c r="D6" t="n">
-        <v>6.97151350996878</v>
+        <v>6.547276017757497</v>
       </c>
       <c r="E6" t="n">
-        <v>15.34660677715647</v>
+        <v>15.06046949903192</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.006362808776009</v>
+        <v>1.199558267014443</v>
       </c>
       <c r="C7" t="n">
-        <v>7.582733598957394</v>
+        <v>8.959858008102547</v>
       </c>
       <c r="D7" t="n">
-        <v>7.379168473184678</v>
+        <v>6.970880976069751</v>
       </c>
       <c r="E7" t="n">
-        <v>16.96826488091808</v>
+        <v>17.13029725118674</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.236940843785439</v>
+        <v>1.255567176363601</v>
       </c>
       <c r="C8" t="n">
-        <v>5.324289916760494</v>
+        <v>10.75179108339962</v>
       </c>
       <c r="D8" t="n">
-        <v>5.608374344899554</v>
+        <v>7.419141087052293</v>
       </c>
       <c r="E8" t="n">
-        <v>12.16960510544549</v>
+        <v>19.42649934681551</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.547406960580967</v>
+        <v>1.298861908082097</v>
       </c>
       <c r="C9" t="n">
-        <v>6.657909340123153</v>
+        <v>12.6396277610444</v>
       </c>
       <c r="D9" t="n">
-        <v>6.074522258392176</v>
+        <v>7.773929889536156</v>
       </c>
       <c r="E9" t="n">
-        <v>14.2798385590963</v>
+        <v>21.71241955866265</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.878008470427901</v>
+        <v>0.8494081137143403</v>
       </c>
       <c r="C10" t="n">
-        <v>8.26631348934251</v>
+        <v>8.899788375923398</v>
       </c>
       <c r="D10" t="n">
-        <v>6.554524389699413</v>
+        <v>6.091361623246802</v>
       </c>
       <c r="E10" t="n">
-        <v>16.69884634946983</v>
+        <v>15.84055811288454</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.200947795875413</v>
+        <v>0.7498981664118837</v>
       </c>
       <c r="C11" t="n">
-        <v>10.02430975314422</v>
+        <v>9.858160667332092</v>
       </c>
       <c r="D11" t="n">
-        <v>7.055606378590482</v>
+        <v>5.937286138542309</v>
       </c>
       <c r="E11" t="n">
-        <v>19.28086392761012</v>
+        <v>16.54534497228628</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.527014246588251</v>
+        <v>0.7665191550447821</v>
       </c>
       <c r="C12" t="n">
-        <v>11.84646304674301</v>
+        <v>11.81082739864787</v>
       </c>
       <c r="D12" t="n">
-        <v>7.568221353889825</v>
+        <v>6.303900183739194</v>
       </c>
       <c r="E12" t="n">
-        <v>21.94169864722109</v>
+        <v>18.88124673743185</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.836040039274214</v>
+        <v>0.5878705253029901</v>
       </c>
       <c r="C13" t="n">
-        <v>13.67912677020678</v>
+        <v>11.23915571046495</v>
       </c>
       <c r="D13" t="n">
-        <v>8.049143663896318</v>
+        <v>5.731276200283157</v>
       </c>
       <c r="E13" t="n">
-        <v>24.56431047337731</v>
+        <v>17.5583024360511</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.63357909248148</v>
+        <v>0.6086639416789376</v>
       </c>
       <c r="C14" t="n">
-        <v>9.445522289760115</v>
+        <v>13.21445172636362</v>
       </c>
       <c r="D14" t="n">
-        <v>6.124073456752305</v>
+        <v>6.045985244356515</v>
       </c>
       <c r="E14" t="n">
-        <v>17.2031748389939</v>
+        <v>19.86910091239907</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.666938879471787</v>
+        <v>0.5656437572788423</v>
       </c>
       <c r="C15" t="n">
-        <v>10.33902069287218</v>
+        <v>14.26377312509374</v>
       </c>
       <c r="D15" t="n">
-        <v>6.146329677207581</v>
+        <v>6.05523330773052</v>
       </c>
       <c r="E15" t="n">
-        <v>18.15228924955155</v>
+        <v>20.8846501901031</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.926012281145477</v>
+        <v>0.5973836605571416</v>
       </c>
       <c r="C16" t="n">
-        <v>12.22708842524852</v>
+        <v>16.48970932988662</v>
       </c>
       <c r="D16" t="n">
-        <v>6.682314836341128</v>
+        <v>6.357680322977834</v>
       </c>
       <c r="E16" t="n">
-        <v>20.83541554273512</v>
+        <v>23.44477331342159</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.543425200800495</v>
+        <v>0.3576899585652829</v>
       </c>
       <c r="C17" t="n">
-        <v>11.27595161442012</v>
+        <v>12.12887438491567</v>
       </c>
       <c r="D17" t="n">
-        <v>6.222012607727968</v>
+        <v>5.250857961209982</v>
       </c>
       <c r="E17" t="n">
-        <v>19.04138942294859</v>
+        <v>17.73742230469093</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.745783037599848</v>
+        <v>0.2686552592671397</v>
       </c>
       <c r="C18" t="n">
-        <v>13.11639476566345</v>
+        <v>10.95115020394711</v>
       </c>
       <c r="D18" t="n">
-        <v>6.654884805484473</v>
+        <v>4.739544121884157</v>
       </c>
       <c r="E18" t="n">
-        <v>21.51706260874777</v>
+        <v>15.9593495850984</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.739892551374367</v>
+        <v>0.3062463788627501</v>
       </c>
       <c r="C19" t="n">
-        <v>13.97316598715964</v>
+        <v>13.44789169547943</v>
       </c>
       <c r="D19" t="n">
-        <v>6.76649970198029</v>
+        <v>5.14381800901595</v>
       </c>
       <c r="E19" t="n">
-        <v>22.4795582405143</v>
+        <v>18.89795608335812</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.92140788441256</v>
+        <v>0.3396945231464389</v>
       </c>
       <c r="C20" t="n">
-        <v>16.03745743244828</v>
+        <v>16.10075070694107</v>
       </c>
       <c r="D20" t="n">
-        <v>7.196927347953221</v>
+        <v>5.554787415490709</v>
       </c>
       <c r="E20" t="n">
-        <v>25.15579266481406</v>
+        <v>21.99523264557822</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.132151452537422</v>
+        <v>0.3663195208856123</v>
       </c>
       <c r="C21" t="n">
-        <v>11.7200746408673</v>
+        <v>18.69507792027552</v>
       </c>
       <c r="D21" t="n">
-        <v>6.023041800508268</v>
+        <v>5.897495904089185</v>
       </c>
       <c r="E21" t="n">
-        <v>18.87526789391299</v>
+        <v>24.95889334525032</v>
       </c>
     </row>
   </sheetData>
